--- a/Bazaar_Sales_Analysis_Final.xlsx
+++ b/Bazaar_Sales_Analysis_Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liamj\Downloads\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FC72278-A709-4591-88DC-3CDE95D0379B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515C55D0-119B-4DBB-9566-FF30C88500BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Final Report" sheetId="8" r:id="rId1"/>
@@ -966,7 +966,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1102,43 +1102,37 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1149,48 +1143,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Abadi"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1352,13 +1304,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -1371,6 +1316,55 @@
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Abadi"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -2470,7 +2464,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-PH"/>
             </a:p>
           </c:txPr>
           <c:dLblPos val="inEnd"/>
@@ -2526,6 +2520,162 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-717F-434D-AEDC-5682AE4E32C9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-717F-434D-AEDC-5682AE4E32C9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-717F-434D-AEDC-5682AE4E32C9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000A-717F-434D-AEDC-5682AE4E32C9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000C-717F-434D-AEDC-5682AE4E32C9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:alpha val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-717F-434D-AEDC-5682AE4E32C9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
@@ -2769,7 +2919,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
+                  <a:endParaRPr lang="en-PH"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="inEnd"/>
@@ -3248,6 +3398,48 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:tint val="77000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:sp3d/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:shade val="76000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:sp3d/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:view3D>
       <c:rotX val="50"/>
@@ -3327,6 +3519,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-73EB-4D9E-8EE0-E1AF9BEDA018}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -3349,6 +3546,11 @@
               </a:effectLst>
               <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-73EB-4D9E-8EE0-E1AF9BEDA018}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -5344,13 +5546,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>14287</xdr:colOff>
+      <xdr:colOff>14286</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>619126</xdr:colOff>
+      <xdr:colOff>657224</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
@@ -5718,7 +5920,7 @@
   <dataFields count="1">
     <dataField name="Sum of Price" fld="2" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
-  <chartFormats count="59">
+  <chartFormats count="61">
     <chartFormat chart="2" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -6246,6 +6448,30 @@
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="71" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="71" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
           </reference>
         </references>
       </pivotArea>
@@ -7404,13 +7630,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6C58D486-4C17-4B02-AB1E-92AE91227BE0}" name="Table1" displayName="Table1" ref="B2:E33" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6C58D486-4C17-4B02-AB1E-92AE91227BE0}" name="Table1" displayName="Table1" ref="B2:E33" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5" totalsRowBorderDxfId="4">
   <autoFilter ref="B2:E33" xr:uid="{6C58D486-4C17-4B02-AB1E-92AE91227BE0}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4F63E892-F48F-4EAB-A110-EC67E536532B}" name="Date" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{28BE0368-9759-4629-956A-F41B205AF356}" name="Product" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{CC2B7E02-C885-45FB-B3C0-AB3265EFA0D8}" name="Price" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{6A72C9C4-7340-4D3E-8010-CEEAF9C02E7F}" name="Customer Type" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{4F63E892-F48F-4EAB-A110-EC67E536532B}" name="Date" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{28BE0368-9759-4629-956A-F41B205AF356}" name="Product" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{CC2B7E02-C885-45FB-B3C0-AB3265EFA0D8}" name="Price" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{6A72C9C4-7340-4D3E-8010-CEEAF9C02E7F}" name="Customer Type" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7740,12 +7966,12 @@
     <col min="3" max="3" width="18.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+    <row r="1" spans="1:1" s="56" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:1" s="58" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:1" s="56" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:XFD2"/>
@@ -7760,12 +7986,8 @@
   <dimension ref="B2:H33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.375" customWidth="1"/>
-    <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="18.75" customWidth="1"/>
+    <col min="7" max="8" width="16.625" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.125" bestFit="1" customWidth="1"/>
@@ -7815,10 +8037,10 @@
       <c r="B4" s="48">
         <v>46067</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="53">
+      <c r="D4" s="21">
         <v>150</v>
       </c>
       <c r="E4" s="51" t="s">
@@ -7855,10 +8077,10 @@
       <c r="B6" s="48">
         <v>46067</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="53">
+      <c r="D6" s="21">
         <v>130</v>
       </c>
       <c r="E6" s="51" t="s">
@@ -7895,10 +8117,10 @@
       <c r="B8" s="48">
         <v>46067</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="53">
+      <c r="D8" s="21">
         <v>150</v>
       </c>
       <c r="E8" s="51" t="s">
@@ -7935,10 +8157,10 @@
       <c r="B10" s="48">
         <v>46067</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="21">
         <v>250</v>
       </c>
       <c r="E10" s="51" t="s">
@@ -7969,10 +8191,10 @@
       <c r="B12" s="48">
         <v>46067</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="21">
         <v>250</v>
       </c>
       <c r="E12" s="51" t="s">
@@ -8006,10 +8228,10 @@
       <c r="B14" s="48">
         <v>46067</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="21">
         <v>130</v>
       </c>
       <c r="E14" s="51" t="s">
@@ -8046,10 +8268,10 @@
       <c r="B16" s="48">
         <v>46067</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="53">
+      <c r="D16" s="21">
         <v>150</v>
       </c>
       <c r="E16" s="51" t="s">
@@ -8080,10 +8302,10 @@
       <c r="B18" s="48">
         <v>46067</v>
       </c>
-      <c r="C18" s="52" t="s">
+      <c r="C18" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="21">
         <v>250</v>
       </c>
       <c r="E18" s="51" t="s">
@@ -8117,10 +8339,10 @@
       <c r="B20" s="48">
         <v>46067</v>
       </c>
-      <c r="C20" s="52" t="s">
+      <c r="C20" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="21">
         <v>150</v>
       </c>
       <c r="E20" s="51" t="s">
@@ -8157,10 +8379,10 @@
       <c r="B22" s="48">
         <v>46067</v>
       </c>
-      <c r="C22" s="52" t="s">
+      <c r="C22" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="53">
+      <c r="D22" s="21">
         <v>150</v>
       </c>
       <c r="E22" s="51" t="s">
@@ -8191,10 +8413,10 @@
       <c r="B24" s="48">
         <v>46068</v>
       </c>
-      <c r="C24" s="52" t="s">
+      <c r="C24" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="53">
+      <c r="D24" s="21">
         <v>240</v>
       </c>
       <c r="E24" s="51" t="s">
@@ -8219,10 +8441,10 @@
       <c r="B26" s="48">
         <v>46068</v>
       </c>
-      <c r="C26" s="52" t="s">
+      <c r="C26" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="53">
+      <c r="D26" s="21">
         <v>130</v>
       </c>
       <c r="E26" s="51" t="s">
@@ -8247,10 +8469,10 @@
       <c r="B28" s="48">
         <v>46068</v>
       </c>
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="53">
+      <c r="D28" s="21">
         <v>240</v>
       </c>
       <c r="E28" s="51" t="s">
@@ -8275,10 +8497,10 @@
       <c r="B30" s="48">
         <v>46068</v>
       </c>
-      <c r="C30" s="52" t="s">
+      <c r="C30" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="53">
+      <c r="D30" s="21">
         <v>240</v>
       </c>
       <c r="E30" s="51" t="s">
@@ -8303,10 +8525,10 @@
       <c r="B32" s="48">
         <v>46068</v>
       </c>
-      <c r="C32" s="52" t="s">
+      <c r="C32" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="53">
+      <c r="D32" s="21">
         <v>240</v>
       </c>
       <c r="E32" s="51" t="s">
@@ -8314,16 +8536,16 @@
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="54">
+      <c r="B33" s="52">
         <v>46068</v>
       </c>
-      <c r="C33" s="55" t="s">
+      <c r="C33" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D33" s="56">
+      <c r="D33" s="54">
         <v>240</v>
       </c>
-      <c r="E33" s="57" t="s">
+      <c r="E33" s="55" t="s">
         <v>7</v>
       </c>
     </row>
@@ -8350,21 +8572,7 @@
   <cols>
     <col min="1" max="1" width="24.875" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="12"/>
-    <col min="3" max="3" width="10.25" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.25" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="12"/>
-    <col min="10" max="10" width="10.25" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.25" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.875" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12" style="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="17" width="18" style="12" customWidth="1"/>
     <col min="18" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
